--- a/example_data/2026-VERSEMENT_LIVREUR_2026.xlsx
+++ b/example_data/2026-VERSEMENT_LIVREUR_2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t xml:space="preserve">DATE</t>
   </si>
@@ -46,31 +46,31 @@
     <t xml:space="preserve">OBSERVATION</t>
   </si>
   <si>
-    <t xml:space="preserve">MOHAMED</t>
+    <t xml:space="preserve">LV – 02</t>
   </si>
   <si>
     <t xml:space="preserve">• 600000 - 161036 = 438964</t>
   </si>
   <si>
-    <t xml:space="preserve">AMINE</t>
+    <t xml:space="preserve">LV – 01</t>
   </si>
   <si>
     <t xml:space="preserve">• -500 Gasoil</t>
   </si>
   <si>
-    <t xml:space="preserve">TOUFIK</t>
+    <t xml:space="preserve">MM</t>
   </si>
   <si>
     <t xml:space="preserve">• 1800 Contrôle Technique</t>
   </si>
   <si>
-    <t xml:space="preserve">REDA</t>
+    <t xml:space="preserve">LV-03</t>
   </si>
   <si>
     <t xml:space="preserve">CREDIT</t>
   </si>
   <si>
-    <t xml:space="preserve">• 12420 Boughrassa (Toufik)
+    <t xml:space="preserve">• 12420 HADJOUTI (Toufik)
 • 16515 Wahab Gouraya (Reda)</t>
   </si>
   <si>
@@ -103,14 +103,11 @@
 • 300 Glaciol</t>
   </si>
   <si>
+    <t xml:space="preserve">LV – 03</t>
+  </si>
+  <si>
     <t xml:space="preserve">• 3000 Farouk Kares (Amine)
 • 15000 La famille Policlinique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Vente au Depos
-  • 970 10 L Bleu
-  • 200 GelDouche
-  • 95 L.Main</t>
   </si>
   <si>
     <t xml:space="preserve">• 28170 Non Chargé
@@ -124,14 +121,10 @@
   <si>
     <t xml:space="preserve">• 1000 Gasoil
 • 250 Glaciol
-• 1770 1 x 4,5 Non chargé</t>
+• 1770: 1 x 4,5 Non chargé</t>
   </si>
   <si>
     <t xml:space="preserve">• 10000 Wahab Gouraya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• 95 Sanibon Vente Au Dépôts
-• 8000 Joint de culasse rendu</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -377,23 +370,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -405,11 +402,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -421,11 +418,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,7 +434,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,19 +442,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -465,15 +462,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -485,39 +482,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -841,640 +834,630 @@
   <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="11.4453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="19.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="53.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="19.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="51.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7" t="n">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="n">
         <v>161036</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="8" t="n">
         <v>161036</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="n">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>0</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>151165</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="8" t="n">
         <v>151165</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="8" t="n">
         <f aca="false">151165-500</f>
         <v>150665</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>0</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>300940</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="8" t="n">
         <v>300940</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="8" t="n">
         <f aca="false">286710+12420</f>
         <v>299130</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>1800</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-10</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>314487</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <f aca="false">297972+16515</f>
         <v>314487</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <f aca="false">297840+16515</f>
         <v>314355</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7" t="n">
+      <c r="F5" s="8"/>
+      <c r="G5" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-132</v>
       </c>
-      <c r="H5" s="8"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11" t="n">
+      <c r="C6" s="11"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="n">
         <f aca="false">-(12420+16515)</f>
         <v>-28935</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="n">
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16" t="n">
         <f aca="false">8265</f>
         <v>8265</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16" t="s">
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="n">
+      <c r="C8" s="18"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="19" t="n">
         <v>46023</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7" t="n">
+      <c r="C9" s="18"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="n">
         <f aca="false">400</f>
         <v>400</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <f aca="false">SUBTOTAL(9,E2:E9)</f>
         <v>904916</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <f aca="false">SUBTOTAL(9,F2:F9)</f>
         <v>2300</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <f aca="false">SUBTOTAL(9,G2:G9)</f>
         <v>-142</v>
       </c>
-      <c r="H10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="25" t="n">
         <v>46025</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27" t="n">
+      <c r="C11" s="27"/>
+      <c r="D11" s="28" t="n">
         <v>219037</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="28" t="n">
         <v>219037</v>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27" t="n">
+      <c r="F11" s="28"/>
+      <c r="G11" s="28" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>0</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="29" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>149100</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="8" t="n">
         <v>149100</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="8" t="n">
         <f aca="false">149100-4080-500-15</f>
         <v>144505</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-4095</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>148375</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="8" t="n">
         <f aca="false">148375</f>
         <v>148375</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="8" t="n">
         <f aca="false">148375-1300-55</f>
         <v>147020</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <f aca="false">1000+300</f>
         <v>1300</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-55</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="6" t="n">
+      <c r="B14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="7" t="n">
         <f aca="false">127653+85835</f>
         <v>213488</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="8" t="n">
         <v>213488</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="8" t="n">
         <f aca="false">207465+5000</f>
         <v>212465</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-23</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15" t="n">
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16" t="n">
         <f aca="false">3000+10000+5000</f>
         <v>18000</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16" t="s">
-        <v>26</v>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7" t="n">
+      <c r="C17" s="18"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
         <v>46025</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7" t="n">
-        <f aca="false">970+200+95</f>
-        <v>1265</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="23" t="n">
         <f aca="false">SUBTOTAL(9,E11:E18)</f>
-        <v>742292</v>
-      </c>
-      <c r="F19" s="22" t="n">
+        <v>741027</v>
+      </c>
+      <c r="F19" s="23" t="n">
         <f aca="false">SUBTOTAL(9,F11:F18)</f>
         <v>2800</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="23" t="n">
         <f aca="false">SUBTOTAL(9,G11:G18)</f>
         <v>-4173</v>
       </c>
-      <c r="H19" s="23"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="25" t="n">
         <v>46026</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="27" t="n">
+      <c r="C20" s="27"/>
+      <c r="D20" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27" t="n">
+      <c r="F20" s="28"/>
+      <c r="G20" s="28" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>0</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>175491</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="8" t="n">
         <f aca="false">147320</f>
         <v>147320</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="8" t="n">
         <f aca="false">147080</f>
         <v>147080</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7" t="n">
+      <c r="F21" s="8"/>
+      <c r="G21" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-240</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>63275</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="8" t="n">
         <v>57965</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="8" t="n">
         <f aca="false">57955</f>
         <v>57955</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7" t="n">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>-10</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="6" t="n">
+      <c r="B23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="7" t="n">
         <f aca="false">155180-60</f>
         <v>155120</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="8" t="n">
         <v>153350</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="8" t="n">
         <f aca="false">153350-1250</f>
         <v>152100</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <f aca="false">1000+250</f>
         <v>1250</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="8" t="n">
         <f aca="false">Tableau15[[#This Row],[CHARGE]]+Tableau15[[#This Row],[VERSEMENT]]-Tableau15[[#This Row],[T.LOGICIEL]]</f>
         <v>0</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7" t="n">
+      <c r="C24" s="18"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15" t="n">
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16" t="s">
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7" t="n">
+      <c r="C26" s="18"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="n">
         <v>46026</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7" t="n">
-        <f aca="false">95+8000</f>
-        <v>8095</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22" t="s">
+      <c r="A28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="23" t="n">
         <f aca="false">SUBTOTAL(9,E20:E27)</f>
-        <v>375230</v>
-      </c>
-      <c r="F28" s="22" t="n">
+        <v>367135</v>
+      </c>
+      <c r="F28" s="23" t="n">
         <f aca="false">SUBTOTAL(9,F20:F27)</f>
         <v>1250</v>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="G28" s="23" t="n">
         <f aca="false">SUBTOTAL(9,G20:G27)</f>
         <v>-250</v>
       </c>
-      <c r="H28" s="23"/>
+      <c r="H28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="33"/>
+      <c r="A29" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="34"/>
       <c r="D29" s="34"/>
       <c r="E29" s="35" t="n">
         <f aca="false">SUBTOTAL(109,Tableau15[VERSEMENT])</f>
-        <v>2022438</v>
+        <v>2013078</v>
       </c>
       <c r="F29" s="35" t="n">
         <f aca="false">SUBTOTAL(109,Tableau15[CHARGE])</f>
